--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -458,7 +458,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>162.84</v>
+        <v>163.06</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>162.84</v>
+        <v>163.06</v>
       </c>
     </row>
   </sheetData>

--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -458,7 +458,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>163.06</v>
+        <v>103.19</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>163.06</v>
+        <v>103.19</v>
       </c>
     </row>
   </sheetData>

--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -458,7 +458,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>103.19</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>103.19</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -458,7 +458,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>83.40000000000001</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>83.40000000000001</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -458,7 +458,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>99.95999999999999</v>
+        <v>77.05</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>99.95999999999999</v>
+        <v>77.05</v>
       </c>
     </row>
   </sheetData>

--- a/result/C101_Test.xlsx
+++ b/result/C101_Test.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="C1GA0" sheetId="1" r:id="rId1"/>
+    <sheet name="C1GA" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -458,24 +458,177 @@
         <v>828.9400000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>77.05</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D5" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>77.20999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D6" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>77.81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D7" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E7" s="3">
+        <v>79.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D8" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E8" s="3">
+        <v>93.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D9" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E9" s="3">
+        <v>110.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3">
-        <v>828.9400000000001</v>
-      </c>
-      <c r="D5" s="3">
-        <v>828.9400000000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>77.05</v>
+      <c r="B10" s="3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D10" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E10" s="3">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D11" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>94.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D12" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E12" s="3">
+        <v>90.77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="D13" s="3">
+        <v>828.9400000000001</v>
+      </c>
+      <c r="E13" s="3">
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>828.9400000000003</v>
+      </c>
+      <c r="D14" s="3">
+        <v>828.9400000000003</v>
+      </c>
+      <c r="E14" s="3">
+        <v>91.536</v>
       </c>
     </row>
   </sheetData>
